--- a/jogos_2024-10-21.xlsx
+++ b/jogos_2024-10-21.xlsx
@@ -633,116 +633,116 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nong Bua Pitchaya</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="O2" t="n">
         <v>3</v>
       </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="P2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S2" t="n">
         <v>3</v>
       </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.7</v>
-      </c>
       <c r="T2" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U2" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V2" t="n">
         <v>1.05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="X2" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="AA2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['14', '21', '43']</t>
+          <t>['12', '30']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['45+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AJ2" t="n">
         <v>2.1</v>
@@ -891,35 +891,35 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Nong Bua Pitchaya</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,80 +927,80 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="M4" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="N4" t="n">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="T4" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V4" t="n">
         <v>1.05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="X4" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['12', '30']</t>
+          <t>['14', '21', '43']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AJ4" t="n">
         <v>2.1</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,22 +1159,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Tyumen</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>3</v>
       </c>
-      <c r="H6" t="n">
-        <v>4</v>
-      </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.84</v>
+        <v>4.01</v>
       </c>
       <c r="M6" t="n">
-        <v>3.73</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="O6" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.33</v>
       </c>
-      <c r="S6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.5</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['18', '45', '68']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.22</v>
       </c>
-      <c r="X6" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y6" t="n">
+      <c r="AI6" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.7</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['16', '21', '84']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>['38', '41', '74', '90+3']</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.62</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45586.45833333334</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,22 +1417,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tyumen</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>2</v>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.01</v>
+        <v>3.84</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4</v>
+        <v>3.73</v>
       </c>
       <c r="N8" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="O8" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="T8" t="n">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W8" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="X8" t="n">
-        <v>2.73</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.07</v>
+        <v>1.7</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.64</v>
+        <v>2.05</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.7</v>
+        <v>2.65</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.03</v>
+        <v>1.62</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '21', '84']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['18', '45', '68']</t>
+          <t>['38', '41', '74', '90+3']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.72</v>
+        <v>2.38</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45586.45833333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rukh Vynnyky</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Karpaty</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>3.15</v>
+        <v>4.33</v>
       </c>
       <c r="O9" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="S9" t="n">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="T9" t="n">
-        <v>2.75</v>
+        <v>3.56</v>
       </c>
       <c r="U9" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="X9" t="n">
-        <v>3.2</v>
+        <v>2.42</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.95</v>
+        <v>3.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.75</v>
+        <v>1.29</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.73</v>
+        <v>2.39</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>1.51</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1635,20 +1635,20 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['43']</t>
+          <t>['47']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" t="n">
         <v>1.62</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45586.5</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
         <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="O10" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="P10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD10" t="n">
         <v>2</v>
       </c>
-      <c r="Q10" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['35', '58']</t>
+          <t>['43']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45586.5</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,109 +1804,109 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
         <v>4.33</v>
       </c>
-      <c r="O11" t="n">
+      <c r="R11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X11" t="n">
         <v>2.75</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Y11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.73</v>
       </c>
-      <c r="Q11" t="n">
-        <v>6</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['47']</t>
+          <t>['35', '58']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3.75</v>
+        <v>2.63</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45586.5</v>
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V14" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W14" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="X14" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AB14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['7']</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
         <v>1.34</v>
       </c>
-      <c r="AC14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>['19', '35', '64', '74']</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['54']</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AI14" t="n">
         <v>1.8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45586.54166666666</v>
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA15" t="n">
         <v>3</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X15" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>['19', '35', '64', '74']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>['54']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AI15" t="n">
         <v>1.8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45586.54166666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,16 +2449,16 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Igman Konjic</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
@@ -2467,7 +2467,7 @@
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,28 +2475,28 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.3</v>
       </c>
-      <c r="M16" t="n">
-        <v>5</v>
-      </c>
-      <c r="N16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.33</v>
-      </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T16" t="n">
         <v>2.5</v>
@@ -2505,53 +2505,53 @@
         <v>1.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="X16" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="AB16" t="n">
         <v>1.39</v>
       </c>
       <c r="AC16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD16" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD16" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['32', '51', '53', '71', '77', '83', '90']</t>
+          <t>['5', '70']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['10']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.02</v>
+        <v>1.23</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.32</v>
+        <v>1.68</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AJ16" t="n">
-        <v>4.05</v>
+        <v>2.5</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45586.54166666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,19 +2578,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Igman Konjic</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.09</v>
+        <v>1.3</v>
       </c>
       <c r="M17" t="n">
-        <v>2.99</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>2.45</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>4.08</v>
+        <v>1.8</v>
       </c>
       <c r="P17" t="n">
-        <v>1.86</v>
+        <v>2.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="S17" t="n">
-        <v>2.43</v>
+        <v>3.25</v>
       </c>
       <c r="T17" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="W17" t="n">
-        <v>1.55</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>2.39</v>
+        <v>3.88</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.54</v>
+        <v>1.61</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.43</v>
+        <v>2.15</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.75</v>
+        <v>2.51</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.1</v>
+        <v>1.39</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['18', '61']</t>
+          <t>['32', '51', '53', '71', '77', '83', '90']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['20', '79']</t>
+          <t>['10']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.53</v>
+        <v>1.02</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.35</v>
+        <v>3.32</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.34</v>
+        <v>1.25</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2</v>
+        <v>4.05</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45586.54166666666</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.83</v>
+        <v>3.09</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>2.99</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="O18" t="n">
-        <v>2.4</v>
+        <v>4.08</v>
       </c>
       <c r="P18" t="n">
-        <v>2.25</v>
+        <v>1.86</v>
       </c>
       <c r="Q18" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="S18" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T18" t="n">
         <v>3.4</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.5</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="V18" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W18" t="n">
-        <v>1.23</v>
+        <v>1.55</v>
       </c>
       <c r="X18" t="n">
-        <v>3.75</v>
+        <v>2.39</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.73</v>
+        <v>2.54</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.08</v>
+        <v>1.43</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.39</v>
+        <v>1.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['5', '70']</t>
+          <t>['18', '61']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>['20', '79']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.23</v>
+        <v>1.53</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.68</v>
+        <v>1.35</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.57</v>
+        <v>2.34</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45586.54166666666</v>
@@ -2836,16 +2836,16 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Akwa United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Katsina United</t>
+          <t>Enugu Rangers</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2862,65 +2862,65 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="M19" t="n">
-        <v>4.14</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>10.34</v>
+        <v>5.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="Q19" t="n">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S19" t="n">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="T19" t="n">
-        <v>3.4</v>
+        <v>3.94</v>
       </c>
       <c r="U19" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="V19" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="X19" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>5.1</v>
+        <v>5.45</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['68']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45586.5625</v>
@@ -2965,16 +2965,16 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Akwa United</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Enugu Rangers</t>
+          <t>Katsina United</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="M20" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="N20" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>11</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="T20" t="n">
         <v>3.4</v>
       </c>
-      <c r="N20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.94</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="V20" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="W20" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="X20" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>5.45</v>
+        <v>5.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
+          <t>['68']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG20" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45586.5625</v>
@@ -3084,35 +3084,35 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Brøndby</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.04</v>
+        <v>2.63</v>
       </c>
       <c r="M21" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>2.84</v>
+        <v>2.55</v>
       </c>
       <c r="O21" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="P21" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
         <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="U21" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="X21" t="n">
-        <v>5.83</v>
+        <v>3.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.42</v>
+        <v>1.9</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="AA21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD21" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['45+2', '55', '88']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45586.58333333334</v>
@@ -3223,109 +3223,109 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N22" t="n">
         <v>3</v>
       </c>
-      <c r="H22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M22" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T22" t="n">
         <v>2.5</v>
       </c>
-      <c r="P22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X22" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD22" t="n">
         <v>2.25</v>
       </c>
-      <c r="U22" t="n">
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.57</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X22" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>['4', '6', '81']</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['90+6']</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AI22" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45586.58333333334</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,25 +3352,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.49</v>
+        <v>1.63</v>
       </c>
       <c r="M23" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="N23" t="n">
-        <v>2.52</v>
+        <v>4.7</v>
       </c>
       <c r="O23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S23" t="n">
         <v>3</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.5</v>
-      </c>
       <c r="T23" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="U23" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="X23" t="n">
-        <v>4.75</v>
+        <v>3.74</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.55</v>
+        <v>1.89</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.25</v>
+        <v>3.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['45+1']</t>
+          <t>['5']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['19']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.58</v>
+        <v>2.45</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45586.58333333334</v>
@@ -3471,35 +3471,35 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G24" t="n">
         <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.13</v>
+        <v>1.5</v>
       </c>
       <c r="M24" t="n">
-        <v>3.34</v>
+        <v>4.2</v>
       </c>
       <c r="N24" t="n">
-        <v>3.12</v>
+        <v>5.7</v>
       </c>
       <c r="O24" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="P24" t="n">
-        <v>2.09</v>
+        <v>2.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.72</v>
+        <v>5.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="T24" t="n">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="W24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['25', '37']</t>
+          <t>['25', '48']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['10', '90+6']</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.82</v>
+        <v>1.36</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.24</v>
+        <v>3.2</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45586.58333333334</v>
@@ -3610,23 +3610,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sandnes Ulf</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>1</v>
       </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.15</v>
+        <v>1.36</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>1.67</v>
+        <v>6.1</v>
       </c>
       <c r="O25" t="n">
-        <v>4.75</v>
+        <v>1.73</v>
       </c>
       <c r="P25" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.1</v>
+        <v>6.5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S25" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="U25" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="V25" t="n">
         <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
-        <v>5.46</v>
+        <v>6.2</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.59</v>
+        <v>3.09</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>1.93</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
+          <t>['19', '70', '79', '86']</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>['83']</t>
-        </is>
-      </c>
       <c r="AG25" t="n">
-        <v>2.35</v>
+        <v>1.03</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.18</v>
+        <v>3.6</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.75</v>
+        <v>1.25</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.4</v>
+        <v>3.75</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45586.58333333334</v>
@@ -3729,29 +3729,29 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Sandnes Ulf</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="N26" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="P26" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="T26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X26" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI26" t="n">
         <v>2.75</v>
       </c>
-      <c r="U26" t="n">
+      <c r="AJ26" t="n">
         <v>1.4</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>['51', '90+2']</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>['80', '82']</t>
-        </is>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.53</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45586.58333333334</v>
@@ -3858,119 +3858,119 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.36</v>
+        <v>2.13</v>
       </c>
       <c r="M27" t="n">
-        <v>5</v>
+        <v>3.34</v>
       </c>
       <c r="N27" t="n">
-        <v>6.1</v>
+        <v>3.12</v>
       </c>
       <c r="O27" t="n">
-        <v>1.73</v>
+        <v>2.7</v>
       </c>
       <c r="P27" t="n">
-        <v>2.88</v>
+        <v>2.09</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.5</v>
+        <v>3.72</v>
       </c>
       <c r="R27" t="n">
-        <v>1.2</v>
+        <v>1.39</v>
       </c>
       <c r="S27" t="n">
-        <v>4.33</v>
+        <v>2.85</v>
       </c>
       <c r="T27" t="n">
-        <v>1.91</v>
+        <v>2.81</v>
       </c>
       <c r="U27" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W27" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="X27" t="n">
-        <v>6.2</v>
+        <v>3.14</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.32</v>
+        <v>1.9</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.09</v>
+        <v>1.81</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.91</v>
+        <v>3.08</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.93</v>
+        <v>1.26</v>
       </c>
       <c r="AC27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>['25', '37']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>['10', '90+6']</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.62</v>
       </c>
-      <c r="AD27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>['19', '70', '79', '86']</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>3.6</v>
-      </c>
       <c r="AI27" t="n">
-        <v>1.25</v>
+        <v>1.82</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3.75</v>
+        <v>2.24</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45586.58333333334</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>BB Bodrumspor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3</v>
+      </c>
+      <c r="O28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>2.3</v>
-      </c>
-      <c r="M28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>['4', '25']</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45586.58333333334</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,19 +4126,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>BB Bodrumspor</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.32</v>
+        <v>1.83</v>
       </c>
       <c r="M29" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="N29" t="n">
+        <v>4</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S29" t="n">
         <v>3</v>
       </c>
-      <c r="O29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.5</v>
-      </c>
       <c r="T29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA29" t="n">
         <v>3.4</v>
       </c>
-      <c r="U29" t="n">
+      <c r="AB29" t="n">
         <v>1.3</v>
       </c>
-      <c r="V29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AC29" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
+          <t>['51', '66']</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>['83']</t>
-        </is>
-      </c>
       <c r="AG29" t="n">
-        <v>1.42</v>
+        <v>1.16</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45586.58333333334</v>
@@ -4245,35 +4245,35 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="M30" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="N30" t="n">
-        <v>4</v>
+        <v>2.84</v>
       </c>
       <c r="O30" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P30" t="n">
         <v>2.5</v>
       </c>
-      <c r="P30" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q30" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="T30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X30" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD30" t="n">
         <v>2.75</v>
       </c>
-      <c r="U30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['51', '66']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+2', '55', '88']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="AH30" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45586.58333333334</v>
@@ -4374,32 +4374,32 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="M31" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N31" t="n">
-        <v>5.7</v>
+        <v>1.83</v>
       </c>
       <c r="O31" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="P31" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U31" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="Z31" t="n">
         <v>2.05</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['25', '48']</t>
+          <t>['51', '90+2']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>['80', '82']</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.36</v>
+        <v>2.6</v>
       </c>
       <c r="AJ31" t="n">
-        <v>3.2</v>
+        <v>1.53</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45586.58333333334</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X32" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>['45+1']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ32" t="n">
         <v>2.05</v>
-      </c>
-      <c r="M32" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N32" t="n">
-        <v>3</v>
-      </c>
-      <c r="O32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X32" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>2.1</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45586.58333333334</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brøndby</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="M33" t="n">
         <v>3.4</v>
       </c>
       <c r="N33" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="O33" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="P33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD33" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U33" t="n">
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>['4', '25']</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
         <v>1.44</v>
       </c>
-      <c r="V33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X33" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>['32']</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AH33" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AI33" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45586.58333333334</v>
@@ -4771,22 +4771,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G34" t="n">
+        <v>3</v>
+      </c>
+      <c r="H34" t="n">
         <v>1</v>
       </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="M34" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="N34" t="n">
-        <v>4.7</v>
+        <v>3.05</v>
       </c>
       <c r="O34" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="P34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T34" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q34" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U34" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="V34" t="n">
         <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="X34" t="n">
-        <v>3.74</v>
+        <v>5.32</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>['4', '6', '81']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+6']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.45</v>
+        <v>1.9</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AJ34" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45586.58333333334</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,23 +5158,23 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
         <v>1</v>
       </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.05</v>
+        <v>1.74</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N37" t="n">
-        <v>3</v>
+        <v>4.29</v>
       </c>
       <c r="O37" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="P37" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="R37" t="n">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="S37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X37" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA37" t="n">
         <v>2.45</v>
       </c>
-      <c r="T37" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X37" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>4</v>
-      </c>
       <c r="AB37" t="n">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
+          <t>['11', '52']</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>['81']</t>
-        </is>
-      </c>
       <c r="AG37" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45586.625</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,22 +5416,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.89</v>
+        <v>3.82</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>4.18</v>
       </c>
       <c r="N39" t="n">
-        <v>3.45</v>
+        <v>1.79</v>
       </c>
       <c r="O39" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="P39" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S39" t="n">
         <v>4</v>
       </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X39" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y39" t="n">
         <v>1.4</v>
       </c>
-      <c r="S39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W39" t="n">
+      <c r="Z39" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH39" t="n">
         <v>1.28</v>
       </c>
-      <c r="X39" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>['13', '30', '40', '72', '90+5']</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AI39" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45586.625</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,22 +5674,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.82</v>
+        <v>1.89</v>
       </c>
       <c r="M41" t="n">
-        <v>4.18</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>1.79</v>
+        <v>3.45</v>
       </c>
       <c r="O41" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q41" t="n">
         <v>4</v>
       </c>
-      <c r="P41" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>2.3</v>
-      </c>
       <c r="R41" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="T41" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="U41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>['13', '30', '40', '72', '90+5']</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AI41" t="n">
         <v>1.67</v>
       </c>
-      <c r="V41" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X41" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI41" t="n">
+      <c r="AJ41" t="n">
         <v>2.4</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.53</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45586.625</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,22 +5803,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.74</v>
+        <v>2.05</v>
       </c>
       <c r="M42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X42" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA42" t="n">
         <v>4</v>
       </c>
-      <c r="N42" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="O42" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P42" t="n">
+      <c r="AB42" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>['81']</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ42" t="n">
         <v>2.4</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X42" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>['11', '52']</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>2.63</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45586.625</v>
@@ -6061,19 +6061,19 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="G44" t="n">
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="M44" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N44" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="O44" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="P44" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q44" t="n">
         <v>4.33</v>
       </c>
       <c r="R44" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="S44" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="T44" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="U44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X44" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>['75']</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
         <v>1.25</v>
       </c>
-      <c r="V44" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W44" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X44" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>['77']</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH44" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AJ44" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45586.64583333334</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,19 +6190,19 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -6216,22 +6216,22 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="M45" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="N45" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="O45" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="P45" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="R45" t="n">
         <v>1.57</v>
@@ -6246,53 +6246,53 @@
         <v>1.25</v>
       </c>
       <c r="V45" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W45" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X45" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>4.85</v>
+        <v>4.65</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>['63']</t>
-        </is>
-      </c>
       <c r="AG45" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.42</v>
+        <v>1.63</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AJ45" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45586.64583333334</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,22 +6319,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -6345,83 +6345,83 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.98</v>
+        <v>2.63</v>
       </c>
       <c r="M46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O46" t="n">
         <v>3.4</v>
       </c>
-      <c r="N46" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="O46" t="n">
-        <v>3.1</v>
-      </c>
       <c r="P46" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="Q46" t="n">
         <v>3.6</v>
       </c>
       <c r="R46" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S46" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="T46" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="U46" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V46" t="n">
         <v>1.06</v>
       </c>
       <c r="W46" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="X46" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.01</v>
+        <v>2.63</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.4</v>
+        <v>4.85</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>['26', '32']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="AI46" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AJ46" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45586.64583333334</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,22 +6448,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -6474,22 +6474,22 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="M47" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N47" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O47" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q47" t="n">
         <v>3.6</v>
-      </c>
-      <c r="O47" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P47" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>4.33</v>
       </c>
       <c r="R47" t="n">
         <v>1.44</v>
@@ -6504,53 +6504,53 @@
         <v>1.33</v>
       </c>
       <c r="V47" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W47" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="X47" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="Y47" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AA47" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC47" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['75']</t>
+          <t>['26', '32']</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AJ47" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45586.64583333334</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6595,70 +6595,70 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M48" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="O48" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P48" t="n">
         <v>2</v>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L48" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="M48" t="n">
+      <c r="Q48" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T48" t="n">
         <v>3.4</v>
       </c>
-      <c r="N48" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="O48" t="n">
+      <c r="U48" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X48" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA48" t="n">
         <v>4.33</v>
       </c>
-      <c r="P48" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S48" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U48" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X48" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AB48" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AC48" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD48" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD48" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AE48" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6666,20 +6666,20 @@
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>['19', '40', '73']</t>
+          <t>['9', '74', '79']</t>
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.18</v>
+        <v>1.63</v>
       </c>
       <c r="AI48" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1.57</v>
+        <v>2.38</v>
       </c>
       <c r="AK48" s="3" t="n">
         <v>45586.65625</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6724,7 +6724,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.35</v>
+        <v>3.45</v>
       </c>
       <c r="M49" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N49" t="n">
-        <v>3.21</v>
+        <v>2.02</v>
       </c>
       <c r="O49" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="P49" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.75</v>
+        <v>2.6</v>
       </c>
       <c r="R49" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S49" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="T49" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X49" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA49" t="n">
         <v>3.4</v>
       </c>
-      <c r="U49" t="n">
+      <c r="AB49" t="n">
         <v>1.3</v>
       </c>
-      <c r="V49" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X49" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AC49" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6795,20 +6795,20 @@
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>['9', '74', '79']</t>
+          <t>['19', '40', '73']</t>
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.63</v>
+        <v>1.18</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="AJ49" t="n">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45586.65625</v>
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Uruguay Primera División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Miramar Misiones</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Deportivo Maldonado</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,65 +6861,65 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.52</v>
+        <v>2.14</v>
       </c>
       <c r="M50" t="n">
-        <v>3.49</v>
+        <v>3.1</v>
       </c>
       <c r="N50" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="O50" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P50" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="R50" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S50" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T50" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U50" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V50" t="n">
         <v>1.08</v>
       </c>
       <c r="W50" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="X50" t="n">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AA50" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -6928,16 +6928,16 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AJ50" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45586.66666666666</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Uruguay Primera División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Miramar Misiones</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,83 +6990,83 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.14</v>
+        <v>2.52</v>
       </c>
       <c r="M51" t="n">
-        <v>3.1</v>
+        <v>3.49</v>
       </c>
       <c r="N51" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="O51" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P51" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q51" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="R51" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S51" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T51" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U51" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V51" t="n">
         <v>1.08</v>
       </c>
       <c r="W51" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="X51" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AA51" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AC51" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AD51" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI51" t="n">
         <v>1.73</v>
       </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>['59']</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG51" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AJ51" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45586.66666666666</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Paraguay Division Profesional</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,109 +7609,109 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Sportivo Luqueño</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Nacional Asunción</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="M56" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N56" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="O56" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P56" t="n">
         <v>2</v>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="M56" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N56" t="n">
-        <v>3</v>
-      </c>
-      <c r="O56" t="n">
+      <c r="Q56" t="n">
         <v>3.4</v>
       </c>
-      <c r="P56" t="n">
+      <c r="R56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S56" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X56" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC56" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q56" t="n">
-        <v>4</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S56" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="T56" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U56" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V56" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W56" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X56" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AD56" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['37', '45+1']</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>['17', '43', '64', '74']</t>
+          <t>['45+4', '67']</t>
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AI56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ56" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>2.3</v>
       </c>
       <c r="AK56" s="3" t="n">
         <v>45586.83333333334</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Paraguay Division Profesional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,109 +7738,109 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sportivo Luqueño</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nacional Asunción</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>4</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
         <v>2</v>
       </c>
-      <c r="H57" t="n">
-        <v>2</v>
-      </c>
-      <c r="I57" t="n">
-        <v>2</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1</v>
-      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="M57" t="n">
-        <v>3.03</v>
+        <v>2.9</v>
       </c>
       <c r="N57" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="O57" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>4</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S57" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T57" t="n">
         <v>3.6</v>
       </c>
-      <c r="P57" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R57" t="n">
+      <c r="U57" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X57" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>['17', '43', '64', '74']</t>
+        </is>
+      </c>
+      <c r="AG57" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH57" t="n">
         <v>1.5</v>
       </c>
-      <c r="S57" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T57" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X57" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC57" t="n">
+      <c r="AI57" t="n">
         <v>1.91</v>
       </c>
-      <c r="AD57" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE57" t="inlineStr">
-        <is>
-          <t>['37', '45+1']</t>
-        </is>
-      </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>['45+4', '67']</t>
-        </is>
-      </c>
-      <c r="AG57" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AJ57" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45586.83333333334</v>
